--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486413_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486413_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4294</v>
+        <v>5.3361</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3203</v>
+        <v>2.9359</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1091</v>
+        <v>2.4002</v>
       </c>
       <c r="G2" t="n">
         <v>3.4166</v>
@@ -610,13 +610,13 @@
         <v>2.8276</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9905</v>
+        <v>1.8972</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6618</v>
+        <v>1.2774</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3287</v>
+        <v>0.6198</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1952</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1127</v>
+        <v>1.7157</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3505</v>
+        <v>-0.6858</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4631</v>
+        <v>2.4015</v>
       </c>
       <c r="G3" t="n">
         <v>0.748</v>
@@ -688,13 +688,13 @@
         <v>2.8276</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7795</v>
+        <v>1.3826</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0911</v>
+        <v>0.7559</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6883</v>
+        <v>0.6267</v>
       </c>
       <c r="V3" t="n">
         <v>1.3252</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1421</v>
+        <v>1.6191</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3326</v>
+        <v>0.6246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8095</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>2.4287</v>
@@ -766,13 +766,13 @@
         <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2192</v>
+        <v>0.2578</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0601</v>
+        <v>0.3521</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2793</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>1.3252</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>F. TERINS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9217</v>
+        <v>1.5341</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5151</v>
+        <v>-1.3749</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4066</v>
+        <v>2.909</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5683</v>
+        <v>1.8925</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0918</v>
+        <v>1.1618</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5235</v>
+        <v>0.7307</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6845</v>
+        <v>1.4479</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5594</v>
+        <v>0.9307</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2439</v>
+        <v>0.5172</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2528</v>
+        <v>0.4446</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5324</v>
+        <v>0.2311</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7204</v>
+        <v>0.2136</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.435</v>
+        <v>-3.2626</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7401</v>
+        <v>2.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1849</v>
+        <v>0.9244</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2656</v>
+        <v>0.4398</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0806</v>
+        <v>0.4846</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. TERINS</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7827</v>
+        <v>0.8909</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1572</v>
+        <v>0.5151</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9399</v>
+        <v>0.3758</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8925</v>
+        <v>-0.5683</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1618</v>
+        <v>-1.0918</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7307</v>
+        <v>0.5235</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4479</v>
+        <v>0.6845</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9307</v>
+        <v>-0.5594</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5172</v>
+        <v>1.2439</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4446</v>
+        <v>-1.2528</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2311</v>
+        <v>-0.5324</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2136</v>
+        <v>-0.7204</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.2626</v>
+        <v>-0.435</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1729</v>
+        <v>0.1541</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3425</v>
+        <v>0.2656</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5154</v>
+        <v>-0.1115</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.411</v>
+        <v>-0.1336</v>
       </c>
       <c r="E7" t="n">
         <v>-1.0712</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6602</v>
+        <v>0.9376</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7316</v>
@@ -1000,13 +1000,13 @@
         <v>2.1751</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4505</v>
+        <v>0.7279</v>
       </c>
       <c r="T7" t="n">
         <v>0.5636</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1131</v>
+        <v>0.1643</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>A. PARRADO CALABRIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2522</v>
+        <v>-1.0097</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4246</v>
+        <v>-0.5629</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6769</v>
+        <v>-0.4468</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9942</v>
+        <v>-0.5608</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.1958</v>
+        <v>-0.0333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2016</v>
+        <v>-0.5275</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1629</v>
+        <v>0.6744</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8514</v>
+        <v>0.8641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6885</v>
+        <v>-0.1896</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.8313</v>
+        <v>-1.2353</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3444</v>
+        <v>-0.8974</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4869</v>
+        <v>-0.3379</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5225</v>
+        <v>2.6101</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1542</v>
+        <v>0.7904</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1971</v>
+        <v>0.3521</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0429</v>
+        <v>0.4383</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9347</v>
+        <v>-1.6743</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3904</v>
+        <v>0.5857</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.3252</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PARRADO CALABRIA</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7796</v>
+        <v>-1.2715</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3019</v>
+        <v>0.3129</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4776</v>
+        <v>-1.5844</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5608</v>
+        <v>-1.9942</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0333</v>
+        <v>-2.1958</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5275</v>
+        <v>0.2016</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6744</v>
+        <v>-0.1629</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8641</v>
+        <v>-0.8514</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1896</v>
+        <v>0.6885</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2353</v>
+        <v>-1.8313</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8974</v>
+        <v>-1.3444</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3379</v>
+        <v>-0.4869</v>
       </c>
       <c r="P9" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.6101</v>
+        <v>1.5225</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0205</v>
+        <v>0.1349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3869</v>
+        <v>0.0853</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4075</v>
+        <v>0.0496</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.6743</v>
+        <v>-0.9347</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5857</v>
+        <v>0.3904</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2599</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1951</v>
+        <v>-1.9794</v>
       </c>
       <c r="E10" t="n">
         <v>-1.7284</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4667</v>
+        <v>-0.251</v>
       </c>
       <c r="G10" t="n">
         <v>0.0878</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3476</v>
+        <v>-0.1319</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1935</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1542</v>
+        <v>0.0616</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1952</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GIL GARCIA</t>
+          <t>A. ALONSO RUIZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2743</v>
+        <v>-2.1188</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0054</v>
+        <v>-0.672</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2689</v>
+        <v>-1.4468</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9489</v>
+        <v>-1.3475</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.478</v>
+        <v>-1.5874</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5291</v>
+        <v>0.2398</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7844</v>
+        <v>0.5172</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6141</v>
+        <v>-0.2095</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3985</v>
+        <v>0.7267</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.7333</v>
+        <v>-1.8648</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8639</v>
+        <v>-1.3779</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8694</v>
+        <v>-0.4869</v>
       </c>
       <c r="P11" t="n">
         <v>-0.87</v>
@@ -1312,28 +1312,28 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3049</v>
+        <v>-0.4663</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2776</v>
+        <v>0.0733</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0273</v>
+        <v>-0.5396</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7602</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.0854</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. ALONSO RUIZ</t>
+          <t>G. GIL GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6459</v>
+        <v>-2.41</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0758</v>
+        <v>-0.0487</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5701</v>
+        <v>-2.3614</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.3475</v>
+        <v>-0.9489</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5874</v>
+        <v>-1.478</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2398</v>
+        <v>0.5291</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5172</v>
+        <v>0.7844</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2095</v>
+        <v>-0.6141</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7267</v>
+        <v>1.3985</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8648</v>
+        <v>-1.7333</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3779</v>
+        <v>-0.8639</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4869</v>
+        <v>-0.8694</v>
       </c>
       <c r="P12" t="n">
         <v>-0.87</v>
@@ -1390,22 +1390,22 @@
         <v>1.5225</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9933</v>
+        <v>0.1691</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3305</v>
+        <v>0.2343</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6629</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-2.0854</v>
       </c>
     </row>
     <row r="13">
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.830499999999998</v>
+        <v>2.1729</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0978</v>
+        <v>-1.7554</v>
       </c>
       <c r="F13" t="n">
-        <v>3.9282</v>
+        <v>3.928199999999998</v>
       </c>
       <c r="G13" t="n">
-        <v>1.422300000000001</v>
+        <v>1.422300000000002</v>
       </c>
       <c r="H13" t="n">
         <v>-2.402500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8249</v>
+        <v>3.824900000000001</v>
       </c>
       <c r="J13" t="n">
         <v>13.8626</v>
@@ -1447,16 +1447,16 @@
         <v>4.7463</v>
       </c>
       <c r="L13" t="n">
-        <v>9.116299999999999</v>
+        <v>9.116300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-12.4403</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.148899999999999</v>
+        <v>-7.1489</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.2914</v>
+        <v>-5.291399999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-4.3503</v>
@@ -1468,13 +1468,13 @@
         <v>21.7507</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4978</v>
+        <v>5.840199999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>3.863499999999999</v>
+        <v>4.2059</v>
       </c>
       <c r="U13" t="n">
-        <v>1.634199999999999</v>
+        <v>1.6343</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7394000000000003</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.1234</v>
+        <v>10.0014</v>
       </c>
       <c r="E14" t="n">
-        <v>7.3945</v>
+        <v>7.2827</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7289</v>
+        <v>2.7187</v>
       </c>
       <c r="G14" t="n">
         <v>5.5597</v>
@@ -1546,13 +1546,13 @@
         <v>2.8276</v>
       </c>
       <c r="S14" t="n">
-        <v>0.411</v>
+        <v>0.289</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.1202</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4194</v>
+        <v>0.4092</v>
       </c>
       <c r="V14" t="n">
         <v>1.3252</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7807</v>
+        <v>3.741</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1704</v>
+        <v>2.5056</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6103</v>
+        <v>1.2354</v>
       </c>
       <c r="G15" t="n">
         <v>2.2686</v>
@@ -1624,13 +1624,13 @@
         <v>2.6101</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0105</v>
+        <v>-0.0502</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.399</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3885</v>
+        <v>0.0135</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6476</v>
+        <v>0.3805</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6081</v>
+        <v>0.161</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0396</v>
+        <v>0.2194</v>
       </c>
       <c r="G16" t="n">
         <v>0.1801</v>
@@ -1702,13 +1702,13 @@
         <v>0.2175</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2501</v>
+        <v>-0.0171</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6081</v>
+        <v>0.161</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.358</v>
+        <v>-0.1782</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3691</v>
+        <v>0.0766</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8259</v>
+        <v>-0.7141</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4567</v>
+        <v>0.7907</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2576</v>
@@ -1780,13 +1780,13 @@
         <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3067</v>
+        <v>-0.861</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.5732</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6218</v>
+        <v>-0.2878</v>
       </c>
       <c r="V17" t="n">
         <v>1.3252</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4061</v>
+        <v>-0.1094</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9054</v>
+        <v>1.0172</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3115</v>
+        <v>-1.1265</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0068</v>
@@ -1858,13 +1858,13 @@
         <v>1.7401</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6168</v>
+        <v>-1.3201</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.399</v>
+        <v>-0.2872</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2178</v>
+        <v>-1.0329</v>
       </c>
       <c r="V18" t="n">
         <v>0.5649999999999999</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9765</v>
+        <v>-2.5332</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9429999999999999</v>
+        <v>-4.4275</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0335</v>
+        <v>1.8942</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9114</v>
+        <v>-1.0773</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4683</v>
+        <v>0.3985</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4431</v>
+        <v>-1.4758</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2387</v>
+        <v>0.6249</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6451</v>
+        <v>0.6998</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5937</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1502</v>
+        <v>-1.7022</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1134</v>
+        <v>-0.3013</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0368</v>
+        <v>-1.4009</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>-5.4377</v>
       </c>
       <c r="R19" t="n">
-        <v>3.0451</v>
+        <v>4.1326</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3476</v>
+        <v>-0.5206</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8857</v>
+        <v>-0.3749</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.538</v>
+        <v>-0.1457</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X19" t="n">
         <v>-0.3904</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1579</v>
+        <v>-2.5883</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.8116</v>
+        <v>1.1256</v>
       </c>
       <c r="F20" t="n">
-        <v>2.6537</v>
+        <v>-3.714</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8198</v>
+        <v>-0.5956</v>
       </c>
       <c r="H20" t="n">
-        <v>2.5852</v>
+        <v>-0.7788</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.405</v>
+        <v>0.1833</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3183</v>
+        <v>2.4391</v>
       </c>
       <c r="K20" t="n">
-        <v>3.0691</v>
+        <v>0.219</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.7507</v>
+        <v>2.2201</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1381</v>
+        <v>-3.0346</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4838</v>
+        <v>-0.9978</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6543</v>
+        <v>-2.0368</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.6101</v>
+        <v>1.7401</v>
       </c>
       <c r="Q20" t="n">
-        <v>-7.6127</v>
+        <v>-1.0875</v>
       </c>
       <c r="R20" t="n">
-        <v>5.0027</v>
+        <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.423</v>
+        <v>-1.0824</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4074</v>
+        <v>-0.2259</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0156</v>
+        <v>-0.8565</v>
       </c>
       <c r="V20" t="n">
-        <v>1.695</v>
+        <v>-2.6504</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8902</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-2.6504</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2834</v>
+        <v>-2.8628</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.8745</v>
+        <v>-1.6135</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5911</v>
+        <v>-1.2493</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0773</v>
+        <v>-1.9114</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3985</v>
+        <v>-0.4683</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4758</v>
+        <v>-1.4431</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6249</v>
+        <v>1.2387</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6998</v>
+        <v>0.6451</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.5937</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7022</v>
+        <v>-3.1502</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3013</v>
+        <v>-1.1134</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4009</v>
+        <v>-2.0368</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-5.4377</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>4.1326</v>
+        <v>3.0451</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2708</v>
+        <v>-0.5387</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>0.2151</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4488</v>
+        <v>-0.7538</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
       <c r="W21" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X21" t="n">
         <v>-0.3904</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3744</v>
+        <v>-2.9717</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6786</v>
+        <v>-5.9233</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.053</v>
+        <v>2.9517</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5956</v>
+        <v>-1.8198</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7788</v>
+        <v>2.5852</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1833</v>
+        <v>-4.405</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4391</v>
+        <v>0.3183</v>
       </c>
       <c r="K22" t="n">
-        <v>0.219</v>
+        <v>3.0691</v>
       </c>
       <c r="L22" t="n">
-        <v>2.2201</v>
+        <v>-2.7507</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.0346</v>
+        <v>-2.1381</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9978</v>
+        <v>-0.4838</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.0368</v>
+        <v>-1.6543</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7401</v>
+        <v>-2.6101</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0875</v>
+        <v>-7.6127</v>
       </c>
       <c r="R22" t="n">
-        <v>2.8276</v>
+        <v>5.0027</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8685</v>
+        <v>-0.2367</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5191</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1956</v>
+        <v>0.2824</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.6504</v>
+        <v>1.695</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.8902</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6504</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8148</v>
+        <v>-3.4744</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2302</v>
+        <v>-3.342</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5846</v>
+        <v>-0.1324</v>
       </c>
       <c r="G23" t="n">
         <v>-2.7622</v>
@@ -2248,13 +2248,13 @@
         <v>1.7401</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0102</v>
+        <v>0.3302</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2656</v>
+        <v>0.1538</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2758</v>
+        <v>0.1763</v>
       </c>
       <c r="V23" t="n">
         <v>-1.695</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.830500000000001</v>
+        <v>-0.3402999999999996</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9282</v>
+        <v>-3.928300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.097699999999999</v>
+        <v>3.587899999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4223</v>
@@ -2317,7 +2317,7 @@
         <v>-9.116299999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>4.3501</v>
+        <v>4.350099999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-21.7505</v>
@@ -2326,16 +2326,16 @@
         <v>26.101</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.497800000000001</v>
+        <v>-4.007600000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-1.6343</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8635</v>
+        <v>-2.3735</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7395999999999991</v>
+        <v>0.7396000000000005</v>
       </c>
       <c r="W24" t="n">
         <v>7.0164</v>
